--- a/Data/Building_profiles_income/Household_assignment_summary.xlsx
+++ b/Data/Building_profiles_income/Household_assignment_summary.xlsx
@@ -1,20 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\PythonProject\Bari_dataset\Data\Building_profiles_income\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4530165E-542C-46D6-BF16-F431220298CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="2370" yWindow="180" windowWidth="22560" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Foglio1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>Census_Section</t>
   </si>
@@ -39,12 +59,30 @@
   <si>
     <t>4_comp_more</t>
   </si>
+  <si>
+    <t>Single retired</t>
+  </si>
+  <si>
+    <t>Single worker</t>
+  </si>
+  <si>
+    <t>Couple retired</t>
+  </si>
+  <si>
+    <t>Working couple</t>
+  </si>
+  <si>
+    <t>3 members</t>
+  </si>
+  <si>
+    <t>4+ members</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,17 +141,901 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF1A3D68"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="it-IT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.24708734076992575"/>
+          <c:y val="2.0524079441209916E-2"/>
+          <c:w val="0.72557928126464499"/>
+          <c:h val="0.96700642061436126"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1A3D68"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="95000"/>
+                        <a:lumOff val="5000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="it-IT"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Foglio1!$A$4:$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Single retired</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Single worker</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Couple retired</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Working couple</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3 members</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4+ members</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Foglio1!$A$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>366</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>339</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>353</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9454-4D5C-9404-267015718CD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="467330496"/>
+        <c:axId val="467322336"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="467330496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="95000"/>
+                    <a:lumOff val="5000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="467322336"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="467322336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="467330496"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="95000"/>
+              <a:lumOff val="5000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="it-IT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>747712</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Grafico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C28ED22-4948-7D2A-0365-D16A4FB42DA6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -151,7 +1073,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -185,6 +1107,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -219,9 +1142,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -394,11 +1318,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -424,7 +1348,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>709</v>
       </c>
@@ -450,7 +1374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>709</v>
       </c>
@@ -476,7 +1400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>709</v>
       </c>
@@ -502,7 +1426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>709</v>
       </c>
@@ -528,7 +1452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>709</v>
       </c>
@@ -554,7 +1478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>709</v>
       </c>
@@ -580,7 +1504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>709</v>
       </c>
@@ -606,7 +1530,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>709</v>
       </c>
@@ -632,7 +1556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>710</v>
       </c>
@@ -658,7 +1582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>710</v>
       </c>
@@ -684,7 +1608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>710</v>
       </c>
@@ -710,7 +1634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>710</v>
       </c>
@@ -736,7 +1660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>710</v>
       </c>
@@ -762,7 +1686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>710</v>
       </c>
@@ -788,7 +1712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>710</v>
       </c>
@@ -814,7 +1738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>710</v>
       </c>
@@ -840,7 +1764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>710</v>
       </c>
@@ -866,7 +1790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>710</v>
       </c>
@@ -892,7 +1816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>710</v>
       </c>
@@ -918,7 +1842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>710</v>
       </c>
@@ -944,7 +1868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>710</v>
       </c>
@@ -970,7 +1894,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>710</v>
       </c>
@@ -996,7 +1920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>710</v>
       </c>
@@ -1022,7 +1946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>710</v>
       </c>
@@ -1048,7 +1972,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>710</v>
       </c>
@@ -1074,7 +1998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>710</v>
       </c>
@@ -1100,7 +2024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>710</v>
       </c>
@@ -1126,7 +2050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>710</v>
       </c>
@@ -1152,7 +2076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>710</v>
       </c>
@@ -1178,7 +2102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>710</v>
       </c>
@@ -1204,7 +2128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>710</v>
       </c>
@@ -1230,7 +2154,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>710</v>
       </c>
@@ -1256,7 +2180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>710</v>
       </c>
@@ -1282,7 +2206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>710</v>
       </c>
@@ -1308,7 +2232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>710</v>
       </c>
@@ -1334,7 +2258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>711</v>
       </c>
@@ -1360,7 +2284,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>711</v>
       </c>
@@ -1386,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>711</v>
       </c>
@@ -1412,7 +2336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>711</v>
       </c>
@@ -1438,7 +2362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>711</v>
       </c>
@@ -1464,7 +2388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>711</v>
       </c>
@@ -1490,7 +2414,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>711</v>
       </c>
@@ -1516,7 +2440,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>711</v>
       </c>
@@ -1542,7 +2466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>711</v>
       </c>
@@ -1568,7 +2492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>711</v>
       </c>
@@ -1594,7 +2518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>711</v>
       </c>
@@ -1620,7 +2544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>711</v>
       </c>
@@ -1646,7 +2570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>711</v>
       </c>
@@ -1672,7 +2596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>711</v>
       </c>
@@ -1698,7 +2622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>711</v>
       </c>
@@ -1724,7 +2648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>711</v>
       </c>
@@ -1750,7 +2674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>711</v>
       </c>
@@ -1776,7 +2700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>711</v>
       </c>
@@ -1802,7 +2726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>711</v>
       </c>
@@ -1828,7 +2752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>711</v>
       </c>
@@ -1854,7 +2778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>711</v>
       </c>
@@ -1880,7 +2804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>711</v>
       </c>
@@ -1906,7 +2830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>711</v>
       </c>
@@ -1932,7 +2856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>712</v>
       </c>
@@ -1958,7 +2882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>712</v>
       </c>
@@ -1984,7 +2908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>712</v>
       </c>
@@ -2010,7 +2934,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>712</v>
       </c>
@@ -2036,7 +2960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>712</v>
       </c>
@@ -2062,7 +2986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>712</v>
       </c>
@@ -2088,7 +3012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>712</v>
       </c>
@@ -2114,7 +3038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>712</v>
       </c>
@@ -2140,7 +3064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>712</v>
       </c>
@@ -2166,7 +3090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>712</v>
       </c>
@@ -2192,7 +3116,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>712</v>
       </c>
@@ -2218,7 +3142,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>712</v>
       </c>
@@ -2244,7 +3168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>713</v>
       </c>
@@ -2270,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>713</v>
       </c>
@@ -2296,7 +3220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>713</v>
       </c>
@@ -2322,7 +3246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>713</v>
       </c>
@@ -2348,7 +3272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>713</v>
       </c>
@@ -2374,7 +3298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>713</v>
       </c>
@@ -2400,7 +3324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>713</v>
       </c>
@@ -2426,7 +3350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>713</v>
       </c>
@@ -2452,7 +3376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>713</v>
       </c>
@@ -2478,7 +3402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>713</v>
       </c>
@@ -2504,7 +3428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>713</v>
       </c>
@@ -2530,7 +3454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>713</v>
       </c>
@@ -2556,7 +3480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>713</v>
       </c>
@@ -2582,7 +3506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>713</v>
       </c>
@@ -2608,7 +3532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>713</v>
       </c>
@@ -2634,7 +3558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>713</v>
       </c>
@@ -2660,7 +3584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>713</v>
       </c>
@@ -2686,7 +3610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>713</v>
       </c>
@@ -2712,7 +3636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>713</v>
       </c>
@@ -2738,7 +3662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>713</v>
       </c>
@@ -2764,7 +3688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>713</v>
       </c>
@@ -2790,7 +3714,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>713</v>
       </c>
@@ -2816,7 +3740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>713</v>
       </c>
@@ -2842,7 +3766,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>713</v>
       </c>
@@ -2868,7 +3792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>713</v>
       </c>
@@ -2894,7 +3818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>713</v>
       </c>
@@ -2920,7 +3844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>713</v>
       </c>
@@ -2946,7 +3870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>713</v>
       </c>
@@ -2972,7 +3896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>714</v>
       </c>
@@ -2998,7 +3922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>714</v>
       </c>
@@ -3024,7 +3948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>714</v>
       </c>
@@ -3050,7 +3974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>714</v>
       </c>
@@ -3076,7 +4000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>714</v>
       </c>
@@ -3102,7 +4026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>714</v>
       </c>
@@ -3128,7 +4052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>714</v>
       </c>
@@ -3154,7 +4078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>714</v>
       </c>
@@ -3180,7 +4104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>714</v>
       </c>
@@ -3206,7 +4130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>714</v>
       </c>
@@ -3232,7 +4156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>714</v>
       </c>
@@ -3261,4 +4185,89 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{671DE7B7-A8E4-4AEC-9415-46D164058293}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <f>SUM(Sheet1!C2:C110)</f>
+        <v>208</v>
+      </c>
+      <c r="B2">
+        <f>SUM(Sheet1!D2:D110)</f>
+        <v>76</v>
+      </c>
+      <c r="C2">
+        <f>SUM(Sheet1!E2:E110)</f>
+        <v>366</v>
+      </c>
+      <c r="D2">
+        <f>SUM(Sheet1!F2:F110)</f>
+        <v>133</v>
+      </c>
+      <c r="E2">
+        <f>SUM(Sheet1!G2:G110)</f>
+        <v>339</v>
+      </c>
+      <c r="F2">
+        <f>SUM(Sheet1!H2:H110)</f>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>